--- a/ci-cd-merge-resolver/repoCollector/datasets/ambari.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/ambari.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="150">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -51,6 +51,417 @@
   </si>
   <si>
     <t>69762201ee278a4be486a1656f3c56a775c24518</t>
+  </si>
+  <si>
+    <t>7ff4a96ca958e0d4b2a41fea5ad7754c5ac4712c</t>
+  </si>
+  <si>
+    <t>b74b05c22f4dec6791e53944a0f6385625e33362</t>
+  </si>
+  <si>
+    <t>2b9a34b0fae681ed3d20459538f2c7711a314b51</t>
+  </si>
+  <si>
+    <t>de4deaf0b04f69692c5226c31ad11deb228b367c</t>
+  </si>
+  <si>
+    <t>b6cf4325ef29a7928131d415432c9bb7271621d5</t>
+  </si>
+  <si>
+    <t>c7cc5607e78991726753ef5d968d6cf2378c5f5b</t>
+  </si>
+  <si>
+    <t>d173011c8b52d99708c842a6d6263b09695b128c</t>
+  </si>
+  <si>
+    <t>ceead22412dc4385fe837884594e5aad57b884d7</t>
+  </si>
+  <si>
+    <t>365c91e92698f6a566b8503486f80c736af79e70</t>
+  </si>
+  <si>
+    <t>45ca79b38e65756dad1095d49670d5b972e060c8</t>
+  </si>
+  <si>
+    <t>f36413f8bbde11f3ffbb22e969e5ff248cd7fc0a</t>
+  </si>
+  <si>
+    <t>67396ba0404319c11094b7376956ab19cfe36341</t>
+  </si>
+  <si>
+    <t>66a5083c5e9434586ef53af647081670596d982c</t>
+  </si>
+  <si>
+    <t>f51351e5437d676ba4c0c7ccf70e91faac004e26</t>
+  </si>
+  <si>
+    <t>dc31e516d95a6636a27d5fbadb9b5529983587c2</t>
+  </si>
+  <si>
+    <t>366f6ca9bd8eec1dd03a735a67158956c2426a31</t>
+  </si>
+  <si>
+    <t>eaf1fd5cee81bc8a021e2dd01ee4fc604c0ee3b0</t>
+  </si>
+  <si>
+    <t>c3150a4652d8b129383a9a49fc3fd78991b224b7</t>
+  </si>
+  <si>
+    <t>af30ab40972022ce4bff6a32b4ebdd29a33ef95d</t>
+  </si>
+  <si>
+    <t>7da02bb9ff07b5934c7a474ce3b4eb5870d0e1a8</t>
+  </si>
+  <si>
+    <t>b4eddc9770eda0e47fe025254ba6143a581a7855</t>
+  </si>
+  <si>
+    <t>17243c68ed31bcc1abd618bffe0426d96da897b7</t>
+  </si>
+  <si>
+    <t>3cefb74cdae3a836ee1896a30dca713e44b95f98</t>
+  </si>
+  <si>
+    <t>19fe4cf1e7450c7230031c660295ec6e04958519</t>
+  </si>
+  <si>
+    <t>0a9a15a2a19856ccd7abe49c529fe9603b124f56</t>
+  </si>
+  <si>
+    <t>48c92cdf6acca316e6a88a3966915cb2a920fcb5</t>
+  </si>
+  <si>
+    <t>58595617f6e4042107e95d81221df14fc8fe9a49</t>
+  </si>
+  <si>
+    <t>ab93e78b5c468836dfcdfb1bff743e815cb6e455</t>
+  </si>
+  <si>
+    <t>591bd9c1140dd76889682ac423b1c0cd96f14b6c</t>
+  </si>
+  <si>
+    <t>c7159a7acc77f3d417c6ff5b817aa04ebbcd68f3</t>
+  </si>
+  <si>
+    <t>8c6590b61927ae7ff858d4c3691032e26de13dd9</t>
+  </si>
+  <si>
+    <t>903a3dee897a6c9f121429a0db9c0db79b0f0ee5</t>
+  </si>
+  <si>
+    <t>0aa22ea8d1482415c85178118d54081dc9e0a0c6</t>
+  </si>
+  <si>
+    <t>903cd1a06c9016efeb3be29c7a323746960ab2e5</t>
+  </si>
+  <si>
+    <t>3adbbadc3ecefee51a3bdc72ff6db1b0dbaa5a75</t>
+  </si>
+  <si>
+    <t>56f05f099aae18d11f849266d14bccf36ae79ad0</t>
+  </si>
+  <si>
+    <t>be73d167a1c3da3053059727e1f6f88d8d624744</t>
+  </si>
+  <si>
+    <t>a670750c39b55178eb9971a24128d5f0e72534c2</t>
+  </si>
+  <si>
+    <t>9d802b7c11a62336fd4de8aa2695af02b061c625</t>
+  </si>
+  <si>
+    <t>6283ae4f688fbbe04cbb904d4469d3b0f9203335</t>
+  </si>
+  <si>
+    <t>c0201e2485009873ec1bb88772aee05ea1c06240</t>
+  </si>
+  <si>
+    <t>f500c9e48d8b9ed7b3aebe547720da9dc9fc10e5</t>
+  </si>
+  <si>
+    <t>12ae2591574c811311b24e2158261a0980548f68</t>
+  </si>
+  <si>
+    <t>fd3220099abd7e990dc18fa9ff9b2758554bb2cf</t>
+  </si>
+  <si>
+    <t>23cc628f4827913869da4917a9bd7b9c0c1abf73</t>
+  </si>
+  <si>
+    <t>21c5c8a0d74b878bfe313a4f3efbf33677b59a24</t>
+  </si>
+  <si>
+    <t>2160d7a0d0255adbe79ab776030654140285114e</t>
+  </si>
+  <si>
+    <t>be703e8a70e63a78a58f5867287c47a380fddda5</t>
+  </si>
+  <si>
+    <t>245afc1b4fa87b6d5ce30f403c15858f90d2ce86</t>
+  </si>
+  <si>
+    <t>7a7f489bc51a0351f9e2c0c1fbb79180319f1d80</t>
+  </si>
+  <si>
+    <t>14acc0ae32a274184830a8e7bf847f5ede8ac953</t>
+  </si>
+  <si>
+    <t>0f266ed6a7b1df2c3d3b18aa49649e12d01b1a4b</t>
+  </si>
+  <si>
+    <t>c4148d805c4145d545712bbce6127e7518a7b7ce</t>
+  </si>
+  <si>
+    <t>1c19200cd446159fba94395867184d2d144c48c7</t>
+  </si>
+  <si>
+    <t>fb2076c718c5bcafb1e83c35a841111d30c6204d</t>
+  </si>
+  <si>
+    <t>138aa48f5f6e21ab7c7ec0636fe12e71a88281b0</t>
+  </si>
+  <si>
+    <t>dc30b4e366f12ce7baa05a2c3dec096175c22f9d</t>
+  </si>
+  <si>
+    <t>d84abbfd303b8860c6f5f241d9c5e993b864c188</t>
+  </si>
+  <si>
+    <t>dcbd826c96b91c718caa519f44663b9a73f17da6</t>
+  </si>
+  <si>
+    <t>8d6a9cc030fb908a002121267ce59ee419ac4b40</t>
+  </si>
+  <si>
+    <t>8938ea219436d78c31934faeeb2c03bdd9f6f415</t>
+  </si>
+  <si>
+    <t>b1f704dfb9b54a57b14ecb5314b65bee7288eeb1</t>
+  </si>
+  <si>
+    <t>80ef77299855f4f1c6a0aceed9cee9ee93c22da1</t>
+  </si>
+  <si>
+    <t>e3d5344a6cf0e22455580cd9a63f8e30256c7097</t>
+  </si>
+  <si>
+    <t>c8858af27daa31bcfc1bef92f6630483c6a1dc41</t>
+  </si>
+  <si>
+    <t>6a0b2a0e2be6901b13db0787fa70ff98905b19da</t>
+  </si>
+  <si>
+    <t>651bdcbdf86c8addace33b1f9bac066633296106</t>
+  </si>
+  <si>
+    <t>51fc3cf77302c7bc04ffb9fdbd53f053b053514f</t>
+  </si>
+  <si>
+    <t>7c9295395923a95ada6e51100b14d1e535590caa</t>
+  </si>
+  <si>
+    <t>353a076c8bf65a911f29b1f908e60d011459ffe0</t>
+  </si>
+  <si>
+    <t>0c3478b1cc98a3738bca05d12a38be87e8711f5b</t>
+  </si>
+  <si>
+    <t>cb030a4e5b829d5adbfbffbb1c02aa94caa6d72b</t>
+  </si>
+  <si>
+    <t>3bd91a2f7968cb182d005a3b45879261297b4495</t>
+  </si>
+  <si>
+    <t>56f838b5b0a5681dffb703f503fcf443cb3b6dbd</t>
+  </si>
+  <si>
+    <t>f516b6c5ad384ceb52181bee6b1553089563182e</t>
+  </si>
+  <si>
+    <t>3acd2e6da46494c175250e4f3a9ec074456b12b9</t>
+  </si>
+  <si>
+    <t>3cb45e849a45b71142eb294a6625d9ec2d5c050a</t>
+  </si>
+  <si>
+    <t>69c55935a57252e3490bfed6905b1bb2fb8ce86d</t>
+  </si>
+  <si>
+    <t>70c23bcd18502095acaa3d0794f877b24a7cab8b</t>
+  </si>
+  <si>
+    <t>3f0752ec09ab7df1831458e26f99a793e433514d</t>
+  </si>
+  <si>
+    <t>77dd10c29b72a9690df1bf09c5ef33b6b3a41977</t>
+  </si>
+  <si>
+    <t>b013be0b97c140b47d77149dcce93ee4f4d90b74</t>
+  </si>
+  <si>
+    <t>9f63871575c5742643035139e1e8a23181ede083</t>
+  </si>
+  <si>
+    <t>358a58871745fb65e93f1e968c03141ee9c6368a</t>
+  </si>
+  <si>
+    <t>0a0e9a5005ef1c410938f6059c0d8f9cb0a16ba5</t>
+  </si>
+  <si>
+    <t>a6639a7c72043ff7bda03e6ba305913c7503193a</t>
+  </si>
+  <si>
+    <t>2c884ab7b8fb935eb47f86d6b5a37c4dc6711252</t>
+  </si>
+  <si>
+    <t>551f17b427465f1a3420a1158fa75f6498fd0fd2</t>
+  </si>
+  <si>
+    <t>eb2c904e1b526e1d581e8985e8e966e3d0ce1eb8</t>
+  </si>
+  <si>
+    <t>6a8115572b328785532aed27c1dc44a1bac17a01</t>
+  </si>
+  <si>
+    <t>36620ba891066619b980814ab02a8de3e3abe5a3</t>
+  </si>
+  <si>
+    <t>341cb1247cbf67f5611766d8f5bf27bd878441e1</t>
+  </si>
+  <si>
+    <t>f2cb1b6ef495d0708024749dfe5b702d270952a2</t>
+  </si>
+  <si>
+    <t>d222f572ee2952add29e60afeb47a4da7ac98685</t>
+  </si>
+  <si>
+    <t>393ab3ee28a27c63084ee4700bf0386b6ceb4a9b</t>
+  </si>
+  <si>
+    <t>132e266521642d90908d3dd69446a701ca94c3db</t>
+  </si>
+  <si>
+    <t>e7399fe9c1f93129e46648ce3f76192bc7e7d3b0</t>
+  </si>
+  <si>
+    <t>90cb3a4ce92c4cfb57356073d1fa603e2403f632</t>
+  </si>
+  <si>
+    <t>e8a6b85de5ead2b9feb8afd0c39fa57eeb5bcc4e</t>
+  </si>
+  <si>
+    <t>532caef33fe65d6933e9797d3db12065555bd69b</t>
+  </si>
+  <si>
+    <t>2c6008293a664ab3b0f24a3f22be54fe0e5f1faf</t>
+  </si>
+  <si>
+    <t>7ed5259d46ce0a0ace7b9d44d13fabe79b737346</t>
+  </si>
+  <si>
+    <t>10cea2c7960beb8b7e92e288c5594eea7d4485bc</t>
+  </si>
+  <si>
+    <t>8985231131061178103423c980c29caee45960c4</t>
+  </si>
+  <si>
+    <t>2c9f0625718ad40361693bc377683af52c93feb0</t>
+  </si>
+  <si>
+    <t>608f0b55ecfe96043ac3bd7bc41e4eb580691fe4</t>
+  </si>
+  <si>
+    <t>48079281714604afd445e6c89de116e49bfab5c0</t>
+  </si>
+  <si>
+    <t>82a64e4985607a961857d74773362e6bf7eb9858</t>
+  </si>
+  <si>
+    <t>cd245c00abaa5720675324a383e691434eabcf32</t>
+  </si>
+  <si>
+    <t>d7f1e8c00e574e5612f40e286b9795bd1e531259</t>
+  </si>
+  <si>
+    <t>a3d7aec0b0e284fdbd0afbc841ff8dcf8216e5cf</t>
+  </si>
+  <si>
+    <t>1cc090d56d2666ec4d96c90509debc65156bce8e</t>
+  </si>
+  <si>
+    <t>3d6ddc2af5de4c489f651eb61984e44e0eb5d04d</t>
+  </si>
+  <si>
+    <t>5467ad0737bdadf23e0cec752acdbdc1b250de3c</t>
+  </si>
+  <si>
+    <t>23fbfe48021fdd739ecc882698bb70fcadb8423b</t>
+  </si>
+  <si>
+    <t>a442efbde22ac635b60b5650df397fd06c147ae1</t>
+  </si>
+  <si>
+    <t>6ae63efd6fdb52aa42795b78a4105e82a2ab96f4</t>
+  </si>
+  <si>
+    <t>47a1bcfea42900076d9791575a3b75a7eeb29ab6</t>
+  </si>
+  <si>
+    <t>108fc4499a545ee6f60eca26eefec7f5192c6b07</t>
+  </si>
+  <si>
+    <t>0fa6d9fda5b77cd6215fc6755591e1fd40206234</t>
+  </si>
+  <si>
+    <t>ee623b7ff2b58c3a957a745a9351c3899e650f9b</t>
+  </si>
+  <si>
+    <t>fb628379aff3042288c75cde11157bd212458a0c</t>
+  </si>
+  <si>
+    <t>e2670f40e13cf49ed9aeef20d6e2ac2dfc8fc3eb</t>
+  </si>
+  <si>
+    <t>5310b95e63b955c697f33413b3af0bce8068f9fc</t>
+  </si>
+  <si>
+    <t>848371dfad55e07de195688895a217ee3ca234f8</t>
+  </si>
+  <si>
+    <t>e06d95d1b779da2762e46de6c8d72a3523498401</t>
+  </si>
+  <si>
+    <t>cbef0c14682ae24f2754063c48ce521c58cdca27</t>
+  </si>
+  <si>
+    <t>083ac6dab5cf59c01da054eb656507c089a54620</t>
+  </si>
+  <si>
+    <t>2eea1bfa9008b0e17dcca8c196ea911fdce041fd</t>
+  </si>
+  <si>
+    <t>4d3839c7f9ce921e92de82bc66440167cb6173a9</t>
+  </si>
+  <si>
+    <t>4fcca627e1094e87ee471a3f21e6d57cadf09b79</t>
+  </si>
+  <si>
+    <t>3265d0b8f2c0c30c5c73bbb1851a909796c574d2</t>
+  </si>
+  <si>
+    <t>f99d821189c00310435e9ec1847bb86ee73bdb8f</t>
+  </si>
+  <si>
+    <t>7bd1a2a3ba0198111d0447b1ff8ec8cf364e9fef</t>
+  </si>
+  <si>
+    <t>fefcdf5db65d07c2f755e40d89823ad799fc6c30</t>
+  </si>
+  <si>
+    <t>ab031a3c8a116d041f96582e5c125d8fca53b795</t>
+  </si>
+  <si>
+    <t>7546f20237ec7c18116edb9f4efda4f5eb9932ca</t>
   </si>
 </sst>
 </file>
@@ -95,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,7 +552,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -156,10 +567,1482 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1.3140000104904175</v>
+        <v>3.487999677658081</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>4.391999244689941</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>4.543000221252441</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>4.285000324249268</v>
+      </c>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>4.496999740600586</v>
+      </c>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>4.26800012588501</v>
+      </c>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="G8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>3.4689998626708984</v>
+      </c>
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>4.134000301361084</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>2.31000018119812</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>1.9620000123977661</v>
+      </c>
+      <c r="J11" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>71.0</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>98.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="G12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>3.728999614715576</v>
+      </c>
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>71.0</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>3.6690003871917725</v>
+      </c>
+      <c r="J13" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>1.9520000219345093</v>
+      </c>
+      <c r="J14" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>514.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>336.0</v>
+      </c>
+      <c r="G15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>2.825000047683716</v>
+      </c>
+      <c r="J15" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D16" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G16" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>3.809000015258789</v>
+      </c>
+      <c r="J16" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D17" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E17" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F17" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G17" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>3.446000099182129</v>
+      </c>
+      <c r="J17" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D18" t="n" s="0">
+        <v>71.0</v>
+      </c>
+      <c r="E18" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F18" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G18" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>3.358999490737915</v>
+      </c>
+      <c r="J18" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D19" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="G19" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>12.966999053955078</v>
+      </c>
+      <c r="J19" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D20" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E20" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="G20" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>12.79800033569336</v>
+      </c>
+      <c r="J20" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D21" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G21" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>12.803999900817871</v>
+      </c>
+      <c r="J21" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D22" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G22" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>10.640999794006348</v>
+      </c>
+      <c r="J22" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D23" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G23" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>11.744000434875488</v>
+      </c>
+      <c r="J23" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D24" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E24" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F24" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G24" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>10.768999099731445</v>
+      </c>
+      <c r="J24" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="D25" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E25" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F25" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G25" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>10.84000015258789</v>
+      </c>
+      <c r="J25" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="D26" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E26" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F26" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G26" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>12.675999641418457</v>
+      </c>
+      <c r="J26" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="D27" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E27" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F27" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G27" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>12.701000213623047</v>
+      </c>
+      <c r="J27" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D28" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E28" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="F28" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="G28" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>11.300000190734863</v>
+      </c>
+      <c r="J28" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D29" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E29" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F29" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G29" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>12.567000389099121</v>
+      </c>
+      <c r="J29" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="D30" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E30" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F30" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G30" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>12.8410005569458</v>
+      </c>
+      <c r="J30" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="D31" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E31" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F31" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G31" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>0.43799999356269836</v>
+      </c>
+      <c r="J31" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D32" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G32" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>10.955000877380371</v>
+      </c>
+      <c r="J32" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="D33" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E33" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F33" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G33" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n" s="0">
+        <v>12.105999946594238</v>
+      </c>
+      <c r="J33" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="D34" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E34" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F34" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G34" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n" s="0">
+        <v>11.069999694824219</v>
+      </c>
+      <c r="J34" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="D35" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E35" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F35" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G35" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n" s="0">
+        <v>0.8789999485015869</v>
+      </c>
+      <c r="J35" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D36" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E36" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F36" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G36" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n" s="0">
+        <v>0.46299999952316284</v>
+      </c>
+      <c r="J36" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="D37" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E37" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F37" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G37" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n" s="0">
+        <v>0.4359999895095825</v>
+      </c>
+      <c r="J37" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D38" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E38" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F38" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G38" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n" s="0">
+        <v>10.311999320983887</v>
+      </c>
+      <c r="J38" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="D39" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E39" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F39" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G39" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n" s="0">
+        <v>12.208999633789062</v>
+      </c>
+      <c r="J39" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D40" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E40" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F40" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G40" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n" s="0">
+        <v>0.3149999976158142</v>
+      </c>
+      <c r="J40" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="D41" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E41" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F41" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G41" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n" s="0">
+        <v>0.2019999921321869</v>
+      </c>
+      <c r="J41" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="D42" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E42" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F42" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G42" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n" s="0">
+        <v>0.6449999809265137</v>
+      </c>
+      <c r="J42" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="D43" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E43" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="F43" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G43" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H43" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n" s="0">
+        <v>0.8550000190734863</v>
+      </c>
+      <c r="J43" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="D44" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G44" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n" s="0">
+        <v>0.38600000739097595</v>
+      </c>
+      <c r="J44" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="D45" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E45" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F45" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G45" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n" s="0">
+        <v>0.32899999618530273</v>
+      </c>
+      <c r="J45" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="D46" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E46" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F46" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G46" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n" s="0">
+        <v>0.19900000095367432</v>
+      </c>
+      <c r="J46" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D47" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E47" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F47" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G47" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n" s="0">
+        <v>0.5860000252723694</v>
+      </c>
+      <c r="J47" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D48" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E48" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F48" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G48" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H48" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n" s="0">
+        <v>0.7200000286102295</v>
+      </c>
+      <c r="J48" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
